--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1403" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1403" uniqueCount="358">
   <si>
     <t>50001558 -  GESVIAL</t>
   </si>
@@ -609,6 +609,9 @@
   </si>
   <si>
     <t>Generacion OC Fabricación Externa ot 4342 -4344,Fabricación estructura proveedor externo ot 4342 -4344</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1215174166542143</t>
@@ -4414,7 +4417,7 @@
         <v>46204.863598842596</v>
       </c>
       <c r="D47" s="9">
-        <v>46204.863616284725</v>
+        <v>46279.14943535879</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>175</v>
@@ -4458,8 +4461,8 @@
       <c r="R47" s="9">
         <v>46286</v>
       </c>
-      <c r="S47" s="7" t="s">
-        <v>33</v>
+      <c r="S47" s="11" t="s">
+        <v>179</v>
       </c>
       <c r="T47" s="10">
         <v>1</v>
@@ -4470,7 +4473,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B48" s="5">
         <v>46169.66919252315</v>
@@ -4515,7 +4518,7 @@
         <v>106</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4525,7 +4528,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B49" s="9">
         <v>46169.66919734953</v>
@@ -4537,7 +4540,7 @@
         <v>46204.8635487037</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
@@ -4570,7 +4573,7 @@
         <v>107</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4580,7 +4583,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46169.66920229167</v>
@@ -4592,16 +4595,16 @@
         <v>46210.65313525463</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46286</v>
@@ -4622,7 +4625,7 @@
         <v>175</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4635,7 +4638,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B51" s="9">
         <v>46169.66924202546</v>
@@ -4647,7 +4650,7 @@
         <v>46256.20687767361</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -4677,7 +4680,7 @@
         <v>112</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P51" s="10" t="s">
         <v>26</v>
@@ -4700,7 +4703,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46169.66924635417</v>
@@ -4739,13 +4742,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>103</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4755,7 +4758,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B53" s="9">
         <v>46169.66925091435</v>
@@ -4767,7 +4770,7 @@
         <v>46199.57082731482</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
@@ -4794,13 +4797,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O53" s="10" t="s">
         <v>104</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4810,7 +4813,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B54" s="5">
         <v>46169.669255659726</v>
@@ -4822,7 +4825,7 @@
         <v>46210.52487434028</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>25</v>
@@ -4846,7 +4849,7 @@
         <v>26</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4863,7 +4866,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B55" s="9">
         <v>46169.66925896991</v>
@@ -4875,16 +4878,16 @@
         <v>46250.346086192134</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I55" s="9">
         <v>46167</v>
@@ -4896,19 +4899,19 @@
         <v>26</v>
       </c>
       <c r="L55" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q55" s="9">
         <v>46167</v>
@@ -4928,7 +4931,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B56" s="5">
         <v>46169.66926408565</v>
@@ -4940,16 +4943,16 @@
         <v>46195.94997940972</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I56" s="5">
         <v>46167</v>
@@ -4967,13 +4970,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>79</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4983,7 +4986,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B57" s="9">
         <v>46169.66926952546</v>
@@ -4995,16 +4998,16 @@
         <v>46195.94998958333</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I57" s="9">
         <v>46167</v>
@@ -5022,13 +5025,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O57" s="10" t="s">
         <v>79</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -5038,7 +5041,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B58" s="5">
         <v>46169.66929263889</v>
@@ -5050,16 +5053,16 @@
         <v>46250.34651130787</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I58" s="5">
         <v>46220</v>
@@ -5077,13 +5080,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q58" s="5">
         <v>46220</v>
@@ -5103,7 +5106,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B59" s="9">
         <v>46169.66929775463</v>
@@ -5115,16 +5118,16 @@
         <v>46195.950096458335</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I59" s="9">
         <v>46181</v>
@@ -5142,13 +5145,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5158,7 +5161,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B60" s="5">
         <v>46169.66930358796</v>
@@ -5170,16 +5173,16 @@
         <v>46196.87985491898</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I60" s="5">
         <v>46181</v>
@@ -5197,13 +5200,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5213,7 +5216,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B61" s="9">
         <v>46169.669327048614</v>
@@ -5231,10 +5234,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I61" s="9">
         <v>46240</v>
@@ -5252,13 +5255,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q61" s="9">
         <v>46240</v>
@@ -5278,7 +5281,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B62" s="5">
         <v>46169.6693399537</v>
@@ -5290,16 +5293,16 @@
         <v>46195.95042396991</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I62" s="5">
         <v>46188</v>
@@ -5320,7 +5323,7 @@
         <v>97</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>97</v>
@@ -5333,7 +5336,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B63" s="9">
         <v>46169.669361203705</v>
@@ -5345,16 +5348,16 @@
         <v>46258.54200784722</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I63" s="9">
         <v>46322</v>
@@ -5372,10 +5375,10 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>26</v>
@@ -5398,7 +5401,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B64" s="5">
         <v>46169.66936501158</v>
@@ -5408,16 +5411,16 @@
         <v>46174.846919421296</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I64" s="5">
         <v>46290</v>
@@ -5435,13 +5438,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5451,7 +5454,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B65" s="9">
         <v>46169.669418136575</v>
@@ -5463,7 +5466,7 @@
         <v>46210.65198340278</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>25</v>
@@ -5487,7 +5490,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P65" s="10" t="s">
         <v>26</v>
@@ -5504,7 +5507,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B66" s="5">
         <v>46169.66942685185</v>
@@ -5516,16 +5519,16 @@
         <v>46260.16864103009</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5543,13 +5546,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>164</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q66" s="5">
         <v>46258</v>
@@ -5569,7 +5572,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B67" s="9">
         <v>46169.669432361115</v>
@@ -5581,16 +5584,16 @@
         <v>46262.197503240735</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I67" s="9">
         <v>46260</v>
@@ -5608,13 +5611,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q67" s="9">
         <v>46260</v>
@@ -5634,7 +5637,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B68" s="5">
         <v>46169.66943836806</v>
@@ -5646,16 +5649,16 @@
         <v>46260.16864224537</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I68" s="5">
         <v>46258</v>
@@ -5673,13 +5676,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>172</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q68" s="5">
         <v>46258</v>
@@ -5699,7 +5702,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B69" s="9">
         <v>46169.669443692124</v>
@@ -5711,16 +5714,16 @@
         <v>46262.19750384259</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I69" s="9">
         <v>46260</v>
@@ -5738,13 +5741,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q69" s="9">
         <v>46260</v>
@@ -5764,7 +5767,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B70" s="5">
         <v>46169.669448368055</v>
@@ -5776,16 +5779,16 @@
         <v>46260.168641122684</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I70" s="5">
         <v>46258</v>
@@ -5803,13 +5806,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q70" s="5">
         <v>46258</v>
@@ -5829,7 +5832,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B71" s="9">
         <v>46169.66945298611</v>
@@ -5841,16 +5844,16 @@
         <v>46262.19750234953</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I71" s="9">
         <v>46260</v>
@@ -5868,13 +5871,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q71" s="9">
         <v>46260</v>
@@ -5894,7 +5897,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B72" s="5">
         <v>46169.66945778935</v>
@@ -5904,7 +5907,7 @@
         <v>46250.35988837963</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>25</v>
@@ -5928,7 +5931,7 @@
         <v>26</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>26</v>
@@ -5941,7 +5944,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B73" s="9">
         <v>46169.66946104167</v>
@@ -5953,16 +5956,16 @@
         <v>46273.14227732639</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I73" s="9">
         <v>46262</v>
@@ -5980,13 +5983,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q73" s="9">
         <v>46262</v>
@@ -6006,7 +6009,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B74" s="5">
         <v>46169.669467280095</v>
@@ -6018,16 +6021,16 @@
         <v>46210.65196928241</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I74" s="5">
         <v>46262</v>
@@ -6045,13 +6048,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6061,7 +6064,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B75" s="9">
         <v>46169.66950289352</v>
@@ -6071,16 +6074,16 @@
         <v>46271.70808619213</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I75" s="9">
         <v>46273</v>
@@ -6098,13 +6101,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q75" s="9">
         <v>46273</v>
@@ -6124,7 +6127,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B76" s="5">
         <v>46169.66950758102</v>
@@ -6134,16 +6137,16 @@
         <v>46209.90937868056</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I76" s="5">
         <v>46273</v>
@@ -6161,13 +6164,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6177,7 +6180,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B77" s="9">
         <v>46169.66953380787</v>
@@ -6187,16 +6190,16 @@
         <v>46271.70811479166</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I77" s="9">
         <v>46294</v>
@@ -6214,13 +6217,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q77" s="9">
         <v>46294</v>
@@ -6240,7 +6243,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B78" s="5">
         <v>46169.66953854167</v>
@@ -6250,16 +6253,16 @@
         <v>46197.84256122685</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -6275,13 +6278,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6291,7 +6294,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B79" s="9">
         <v>46169.66960108797</v>
@@ -6303,7 +6306,7 @@
         <v>46252.610598287036</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>25</v>
@@ -6327,7 +6330,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>26</v>
@@ -6344,7 +6347,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B80" s="5">
         <v>46169.66960956018</v>
@@ -6356,16 +6359,16 @@
         <v>46209.844928101855</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I80" s="5">
         <v>46174</v>
@@ -6383,13 +6386,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>133</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q80" s="5">
         <v>46174</v>
@@ -6409,7 +6412,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B81" s="9">
         <v>46169.6696165162</v>
@@ -6421,16 +6424,16 @@
         <v>46209.84471936343</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I81" s="9">
         <v>46288</v>
@@ -6448,13 +6451,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>124</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q81" s="9">
         <v>46288</v>
@@ -6474,7 +6477,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B82" s="5">
         <v>46169.669622939815</v>
@@ -6486,16 +6489,16 @@
         <v>46209.85430440972</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I82" s="5">
         <v>46308</v>
@@ -6513,13 +6516,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>142</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q82" s="5">
         <v>46308</v>
@@ -6539,7 +6542,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B83" s="9">
         <v>46169.66962980324</v>
@@ -6551,16 +6554,16 @@
         <v>46239.59650748843</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I83" s="9">
         <v>46287</v>
@@ -6578,13 +6581,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q83" s="9">
         <v>46287</v>
@@ -6604,7 +6607,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B84" s="5">
         <v>46169.669635185186</v>
@@ -6622,10 +6625,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I84" s="5">
         <v>46220</v>
@@ -6643,13 +6646,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>153</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q84" s="5">
         <v>46220</v>
@@ -6669,17 +6672,17 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B85" s="9">
         <v>46169.66964790509</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46252.61072833333</v>
+        <v>46279.37673079861</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>25</v>
@@ -6703,7 +6706,7 @@
         <v>26</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6716,7 +6719,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B86" s="5">
         <v>46169.66965109954</v>
@@ -6728,7 +6731,7 @@
         <v>46252.61067681713</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6755,13 +6758,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q86" s="5">
         <v>46294</v>
@@ -6781,7 +6784,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B87" s="9">
         <v>46169.6696568287</v>
@@ -6791,7 +6794,7 @@
         <v>46239.59649744213</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6818,13 +6821,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6834,7 +6837,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B88" s="5">
         <v>46169.669688622685</v>
@@ -6846,7 +6849,7 @@
         <v>46250.36067016204</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6873,13 +6876,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q88" s="5">
         <v>46316</v>
@@ -6899,7 +6902,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B89" s="9">
         <v>46169.66969347223</v>
@@ -6909,7 +6912,7 @@
         <v>46223.83603929398</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6934,13 +6937,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6950,7 +6953,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B90" s="5">
         <v>46169.66972681713</v>
@@ -6962,7 +6965,7 @@
         <v>46250.36077557871</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6989,13 +6992,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q90" s="5">
         <v>46317</v>
@@ -7015,7 +7018,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B91" s="9">
         <v>46169.66973180555</v>
@@ -7025,7 +7028,7 @@
         <v>46223.56782162037</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -7052,13 +7055,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7068,7 +7071,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B92" s="5">
         <v>46169.66981054399</v>
@@ -7080,7 +7083,7 @@
         <v>46252.61073834491</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7107,13 +7110,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q92" s="5">
         <v>46318</v>
@@ -7133,7 +7136,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B93" s="9">
         <v>46169.66981724537</v>
@@ -7143,7 +7146,7 @@
         <v>46223.56789047454</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7170,13 +7173,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7186,7 +7189,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B94" s="5">
         <v>46169.669861041664</v>
@@ -7196,7 +7199,7 @@
         <v>46260.58797681713</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7223,13 +7226,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q94" s="5">
         <v>46321</v>
@@ -7249,7 +7252,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B95" s="9">
         <v>46169.66986724537</v>
@@ -7259,7 +7262,7 @@
         <v>46223.56796597222</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7286,13 +7289,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7302,7 +7305,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B96" s="5">
         <v>46169.66990296297</v>
@@ -7312,7 +7315,7 @@
         <v>46260.58799998843</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7339,13 +7342,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q96" s="5">
         <v>46323</v>
@@ -7365,7 +7368,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B97" s="9">
         <v>46169.66994555556</v>
@@ -7375,7 +7378,7 @@
         <v>46223.836147291666</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7400,13 +7403,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7416,7 +7419,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B98" s="5">
         <v>46169.669978645834</v>
@@ -7426,7 +7429,7 @@
         <v>46252.61088775463</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>25</v>
@@ -7450,7 +7453,7 @@
         <v>26</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>26</v>
@@ -7463,7 +7466,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B99" s="9">
         <v>46169.66998244213</v>
@@ -7475,16 +7478,16 @@
         <v>46252.61081997685</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I99" s="9">
         <v>46324</v>
@@ -7502,13 +7505,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q99" s="9">
         <v>46324</v>
@@ -7528,7 +7531,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B100" s="5">
         <v>46169.66998994213</v>
@@ -7538,16 +7541,16 @@
         <v>46174.84838837963</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I100" s="6"/>
       <c r="J100" s="5">
@@ -7563,13 +7566,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7579,7 +7582,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B101" s="9">
         <v>46170.63118891204</v>
@@ -7589,16 +7592,16 @@
         <v>46209.90833168982</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
@@ -7614,13 +7617,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7630,7 +7633,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B102" s="5">
         <v>46174.820955891206</v>
@@ -7646,10 +7649,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I102" s="5">
         <v>46324</v>
@@ -7667,13 +7670,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>64</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7683,7 +7686,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B103" s="9">
         <v>46169.670044224535</v>
@@ -7693,7 +7696,7 @@
         <v>46260.58802633102</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7718,13 +7721,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q103" s="9">
         <v>46325</v>
@@ -7744,7 +7747,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B104" s="5">
         <v>46169.670049050925</v>
@@ -7754,7 +7757,7 @@
         <v>46223.568262175926</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7779,13 +7782,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7795,7 +7798,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B105" s="9">
         <v>46170.63213679398</v>
@@ -7805,7 +7808,7 @@
         <v>46223.56826151621</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7830,13 +7833,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7846,7 +7849,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B106" s="5">
         <v>46174.82099290509</v>
@@ -7856,7 +7859,7 @@
         <v>46223.5682608912</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7883,7 +7886,7 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>64</v>
@@ -7899,7 +7902,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B107" s="9">
         <v>46169.67013976852</v>
@@ -7911,16 +7914,16 @@
         <v>46252.61090652778</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I107" s="10"/>
       <c r="J107" s="9">
@@ -7936,13 +7939,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q107" s="9">
         <v>46328</v>
@@ -7962,7 +7965,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B108" s="5">
         <v>46169.670151377315</v>
@@ -7972,16 +7975,16 @@
         <v>46174.848669872685</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I108" s="5">
         <v>46328</v>
@@ -7999,13 +8002,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8015,7 +8018,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B109" s="9">
         <v>46170.63285997685</v>
@@ -8025,16 +8028,16 @@
         <v>46174.848667314815</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I109" s="9">
         <v>46328</v>
@@ -8052,13 +8055,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -8068,7 +8071,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B110" s="5">
         <v>46174.821024143515</v>
@@ -8084,10 +8087,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I110" s="5">
         <v>46328</v>
@@ -8105,10 +8108,10 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>64</v>
@@ -8121,7 +8124,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B111" s="9">
         <v>46169.67021965278</v>
@@ -8131,16 +8134,16 @@
         <v>46253.62502890047</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I111" s="9">
         <v>46329</v>
@@ -8158,13 +8161,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q111" s="9">
         <v>46329</v>
@@ -8184,7 +8187,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B112" s="5">
         <v>46169.67022677083</v>
@@ -8194,16 +8197,16 @@
         <v>46174.84878571759</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I112" s="6"/>
       <c r="J112" s="5">
@@ -8219,13 +8222,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8235,7 +8238,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B113" s="9">
         <v>46170.633581828704</v>
@@ -8245,16 +8248,16 @@
         <v>46174.84878314815</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I113" s="10"/>
       <c r="J113" s="9">
@@ -8270,10 +8273,10 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8286,7 +8289,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B114" s="5">
         <v>46174.821057037036</v>
@@ -8302,10 +8305,10 @@
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I114" s="6"/>
       <c r="J114" s="5">
@@ -8321,7 +8324,7 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>64</v>
@@ -8337,7 +8340,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B115" s="9">
         <v>46169.67031616898</v>
@@ -8347,7 +8350,7 @@
         <v>46174.82401751158</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>25</v>
@@ -8371,7 +8374,7 @@
         <v>26</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P115" s="10" t="s">
         <v>26</v>
@@ -8384,7 +8387,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B116" s="5">
         <v>46169.67031976852</v>
@@ -8394,16 +8397,16 @@
         <v>46174.84885483797</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="I116" s="5">
         <v>46330</v>
@@ -8421,13 +8424,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q116" s="5">
         <v>46330</v>
@@ -8447,7 +8450,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B117" s="9">
         <v>46169.6703253125</v>
@@ -8457,7 +8460,7 @@
         <v>46192.97339644676</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8484,13 +8487,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q117" s="9">
         <v>46330</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -431,6 +431,9 @@
     <t>Fabricación Alabe  ot 4342,Generación OC Alabe  ot 4342</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1215174266235843</t>
   </si>
   <si>
@@ -609,9 +612,6 @@
   </si>
   <si>
     <t>Generacion OC Fabricación Externa ot 4342 -4344,Fabricación estructura proveedor externo ot 4342 -4344</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1215174166542143</t>
@@ -3260,7 +3260,7 @@
         <v>46182.63465045139</v>
       </c>
       <c r="D28" s="5">
-        <v>46182.63466408565</v>
+        <v>46280.150507962964</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>115</v>
@@ -3304,8 +3304,8 @@
       <c r="R28" s="5">
         <v>46287</v>
       </c>
-      <c r="S28" s="7" t="s">
-        <v>33</v>
+      <c r="S28" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="T28" s="6">
         <v>1</v>
@@ -3316,7 +3316,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B29" s="9">
         <v>46169.66909520833</v>
@@ -3328,7 +3328,7 @@
         <v>46182.63236322917</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
@@ -3361,7 +3361,7 @@
         <v>88</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3372,12 +3372,12 @@
         <v>0</v>
       </c>
       <c r="U29" s="12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B30" s="5">
         <v>46169.669100810184</v>
@@ -3389,7 +3389,7 @@
         <v>46182.63463722222</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3419,10 +3419,10 @@
         <v>115</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3433,12 +3433,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B31" s="9">
         <v>46169.669106284724</v>
@@ -3450,7 +3450,7 @@
         <v>46182.63460042824</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
@@ -3480,7 +3480,7 @@
         <v>112</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P31" s="10" t="s">
         <v>112</v>
@@ -3503,7 +3503,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B32" s="5">
         <v>46169.66911128472</v>
@@ -3515,7 +3515,7 @@
         <v>46182.6318109375</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3542,13 +3542,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>91</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3559,12 +3559,12 @@
         <v>0</v>
       </c>
       <c r="U32" s="12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B33" s="9">
         <v>46169.669116805555</v>
@@ -3576,7 +3576,7 @@
         <v>46182.63457327546</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
@@ -3603,13 +3603,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3620,12 +3620,12 @@
         <v>0</v>
       </c>
       <c r="U33" s="12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B34" s="5">
         <v>46169.66912204861</v>
@@ -3637,7 +3637,7 @@
         <v>46182.6344355787</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3667,7 +3667,7 @@
         <v>112</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>112</v>
@@ -3690,7 +3690,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B35" s="9">
         <v>46169.66912711806</v>
@@ -3702,7 +3702,7 @@
         <v>46182.63203959491</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
@@ -3729,13 +3729,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O35" s="10" t="s">
         <v>85</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3746,12 +3746,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B36" s="5">
         <v>46169.66913270833</v>
@@ -3763,7 +3763,7 @@
         <v>46182.634411203704</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3790,13 +3790,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3807,12 +3807,12 @@
         <v>0</v>
       </c>
       <c r="U36" s="12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B37" s="9">
         <v>46169.66913809028</v>
@@ -3824,7 +3824,7 @@
         <v>46182.6343528588</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
@@ -3851,13 +3851,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3868,12 +3868,12 @@
         <v>0</v>
       </c>
       <c r="U37" s="12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B38" s="5">
         <v>46169.66914475695</v>
@@ -3885,7 +3885,7 @@
         <v>46239.596476666666</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -3915,7 +3915,7 @@
         <v>112</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3938,7 +3938,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B39" s="9">
         <v>46169.669149270834</v>
@@ -3977,13 +3977,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O39" s="10" t="s">
         <v>109</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -3993,7 +3993,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B40" s="5">
         <v>46169.66915408565</v>
@@ -4003,7 +4003,7 @@
         <v>46219.16855109954</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
@@ -4030,13 +4030,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>110</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4046,7 +4046,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B41" s="9">
         <v>46169.66915865741</v>
@@ -4058,16 +4058,16 @@
         <v>46256.206877731485</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I41" s="9">
         <v>46245</v>
@@ -4088,7 +4088,7 @@
         <v>112</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>112</v>
@@ -4111,7 +4111,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B42" s="5">
         <v>46169.66916377315</v>
@@ -4123,16 +4123,16 @@
         <v>46199.56927892361</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I42" s="5">
         <v>46245</v>
@@ -4150,13 +4150,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>96</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4167,12 +4167,12 @@
         <v>0</v>
       </c>
       <c r="U42" s="12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B43" s="9">
         <v>46169.66916960648</v>
@@ -4184,16 +4184,16 @@
         <v>46205.61247092593</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I43" s="9">
         <v>46247</v>
@@ -4211,13 +4211,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4228,12 +4228,12 @@
         <v>0</v>
       </c>
       <c r="U43" s="12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B44" s="5">
         <v>46169.66917503472</v>
@@ -4245,16 +4245,16 @@
         <v>46256.206877951394</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I44" s="5">
         <v>46245</v>
@@ -4275,7 +4275,7 @@
         <v>112</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4298,7 +4298,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B45" s="9">
         <v>46169.669178888886</v>
@@ -4316,10 +4316,10 @@
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I45" s="9">
         <v>46245</v>
@@ -4337,13 +4337,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>100</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4353,7 +4353,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B46" s="5">
         <v>46169.669183680555</v>
@@ -4365,16 +4365,16 @@
         <v>46199.56984034722</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I46" s="5">
         <v>46247</v>
@@ -4392,13 +4392,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>101</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4408,7 +4408,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B47" s="9">
         <v>46169.66918849537</v>
@@ -4420,16 +4420,16 @@
         <v>46279.14943535879</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I47" s="9">
         <v>46245</v>
@@ -4450,7 +4450,7 @@
         <v>112</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>26</v>
@@ -4462,7 +4462,7 @@
         <v>46286</v>
       </c>
       <c r="S47" s="11" t="s">
-        <v>179</v>
+        <v>119</v>
       </c>
       <c r="T47" s="10">
         <v>1</v>
@@ -4491,10 +4491,10 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I48" s="5">
         <v>46245</v>
@@ -4512,7 +4512,7 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>106</v>
@@ -4546,10 +4546,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I49" s="9">
         <v>46254</v>
@@ -4567,7 +4567,7 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O49" s="10" t="s">
         <v>107</v>
@@ -4622,7 +4622,7 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>183</v>
@@ -4656,10 +4656,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I51" s="9">
         <v>46245</v>
@@ -4721,10 +4721,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I52" s="5">
         <v>46245</v>
@@ -4776,10 +4776,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I53" s="9">
         <v>46247</v>
@@ -5549,7 +5549,7 @@
         <v>232</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>238</v>
@@ -5679,7 +5679,7 @@
         <v>232</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>245</v>
@@ -6389,7 +6389,7 @@
         <v>232</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>242</v>
@@ -6454,7 +6454,7 @@
         <v>232</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P81" s="10" t="s">
         <v>278</v>
@@ -6519,7 +6519,7 @@
         <v>232</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>278</v>
@@ -6551,7 +6551,7 @@
         <v>46239.596492094905</v>
       </c>
       <c r="D83" s="9">
-        <v>46239.59650748843</v>
+        <v>46280.15050829861</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>282</v>
@@ -6595,8 +6595,8 @@
       <c r="R83" s="9">
         <v>46287</v>
       </c>
-      <c r="S83" s="7" t="s">
-        <v>33</v>
+      <c r="S83" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="T83" s="10">
         <v>1</v>
@@ -6649,7 +6649,7 @@
         <v>232</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>285</v>
@@ -8182,7 +8182,7 @@
         <v>0</v>
       </c>
       <c r="U111" s="12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
@@ -8445,7 +8445,7 @@
         <v>0</v>
       </c>
       <c r="U116" s="12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
@@ -8508,7 +8508,7 @@
         <v>0</v>
       </c>
       <c r="U117" s="12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -6421,7 +6421,7 @@
         <v>46209.844589050925</v>
       </c>
       <c r="D81" s="9">
-        <v>46209.84471936343</v>
+        <v>46281.161886574075</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>277</v>
@@ -6465,8 +6465,8 @@
       <c r="R81" s="9">
         <v>46288</v>
       </c>
-      <c r="S81" s="7" t="s">
-        <v>33</v>
+      <c r="S81" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="T81" s="10">
         <v>1</v>
